--- a/PAMaap/app/archives/XLXS_IMPORT/ALIMENTADORES/INVENTARIO_AD_beta.xlsx
+++ b/PAMaap/app/archives/XLXS_IMPORT/ALIMENTADORES/INVENTARIO_AD_beta.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XimenaVanegas\Pictures\autompython\AutoM_python\Excel\ARCHIVOS_ALIMENTADORES_INFRA_AD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\autompython\PAMaap\app\archives\XLXS_IMPORT\ALIMENTADORES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B7546F-7747-4FA3-9394-67A14D6EF481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040"/>
   </bookViews>
   <sheets>
     <sheet name="AD" sheetId="1" r:id="rId1"/>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
   <si>
     <t>TIPO_SERVER</t>
   </si>
@@ -309,7 +308,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -335,7 +334,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -358,6 +357,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -365,12 +377,71 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFFF0000"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -381,6 +452,18 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:C1048576" totalsRowShown="0" headerRowDxfId="1" headerRowBorderDxfId="2" tableBorderDxfId="3">
+  <autoFilter ref="A1:C1048576"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="NOMBRE SERVERS"/>
+    <tableColumn id="2" name="DOLIENTE"/>
+    <tableColumn id="3" name="TIPO_SERVER"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -679,13 +762,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1634,17 +1717,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>90</v>
-      </c>
-    </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>90</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A1:A86 A88:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>